--- a/QA_Dataset_1000_Chatbot.xlsx
+++ b/QA_Dataset_1000_Chatbot.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\doc-sheet-chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D6FEBD-7EDD-4A53-82E8-A50D84A20E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD949DC9-6330-4138-A081-E4B71E99F579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QA_Dataset_1000" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1182">
   <si>
     <t>ลำดับข้อ</t>
   </si>
@@ -3428,6 +3441,309 @@
   </si>
   <si>
     <t>สรุปวิธีและแนวทางปฏิบัติของ การจัดทำแผนการจัดการเรียนรู้ของครูอาชีวศึกษา สอดคล้องและสัมพันธ์กับหนังสือการออกแบบการจัดการเรียนรู้ของ ศ.ดร.ชัยวัฒน์ สุทธิรัตน์ ให้ทีครับ/ค่ะ</t>
+  </si>
+  <si>
+    <t>แผนการสอนนี้เป็นของสถาบันหรือหน่วยงานใด?</t>
+  </si>
+  <si>
+    <t>แบบฟอร์มแผนการสอน คณะครุศาสตร์อุตสาหกรรม มจพ. มีโครงสร้างส่วนหัวอย่างไร?</t>
+  </si>
+  <si>
+    <t>ข้อมูลพื้นฐานส่วนหัวของแบบฟอร์มแผนการสอน มจพ. มีอะไรบ้าง?</t>
+  </si>
+  <si>
+    <t>ในแบบฟอร์มระบุระดับชั้นเรียนและกลุ่มเรียนตัวอย่างเป็นอะไร?</t>
+  </si>
+  <si>
+    <t>เวลาในการสอนในแบบฟอร์มกำหนดหน่วยเป็นอะไร?</t>
+  </si>
+  <si>
+    <t>ส่วนหัวของแผนการสอนต้องระบุชื่อผู้สอนและปีการศึกษาหรือไม่?</t>
+  </si>
+  <si>
+    <t>วัตถุประสงค์ในแผนการสอนระบุเป็นประเภทใด?</t>
+  </si>
+  <si>
+    <t>การเขียนวัตถุประสงค์เชิงพฤติกรรมในแผนการสอนมีข้อความนำอย่างไร?</t>
+  </si>
+  <si>
+    <t>ในแบบฟอร์มให้จับคู่วัตถุประสงค์เชิงพฤติกรรมกับการประเมินส่วนใด?</t>
+  </si>
+  <si>
+    <t>การประเมินขั้นสำเร็จผลในแผนการสอนมีความสัมพันธ์กับวัตถุประสงค์อย่างไร?</t>
+  </si>
+  <si>
+    <t>วัตถุประสงค์เชิงพฤติกรรมในแบบฟอร์มเว้นไว้กี่ข้อ?</t>
+  </si>
+  <si>
+    <t>ช่อง 'ความรู้พื้นฐานที่จำเป็น' มีไว้สำหรับระบุอะไร?</t>
+  </si>
+  <si>
+    <t>ช่อง 'การนำเข้าสู่บทเรียน' มีความสำคัญอย่างไรในแผน?</t>
+  </si>
+  <si>
+    <t>ทำไมแผนการสอนต้องระบุความรู้พื้นฐานที่จำเป็นก่อนเริ่มสอน?</t>
+  </si>
+  <si>
+    <t>รูปแบบขั้นตอนการสอนหลักในตารางปฏิบัติการมีกี่ขั้นตอน อะไรบ้าง?</t>
+  </si>
+  <si>
+    <t>ขั้นบอกกล่าวใช้ตัวอักษรย่อภาษาอังกฤษว่าอะไร?</t>
+  </si>
+  <si>
+    <t>ขั้นพยายามใช้ตัวอักษรย่อภาษาอังกฤษว่าอะไร?</t>
+  </si>
+  <si>
+    <t>ขั้นสำเร็จผลใช้ตัวอักษรย่อภาษาอังกฤษว่าอะไร?</t>
+  </si>
+  <si>
+    <t>เป็นแบบฟอร์มแผนการสอนของ คณะครุศาสตร์อุตสาหกรรม มหาวิทยาลัยเทคโนโลยีพระจอมเกล้าพระนครเหนือ (มจพ.)</t>
+  </si>
+  <si>
+    <t>ระบุชื่อสถาบัน คณะครุศาสตร์อุตสาหกรรม มจพ., เรื่อง, วิชา, เวลาในการสอน (นาที), ชั้นเรียน, วันที่สอน, ผู้สอน, ชั้น/กลุ่มเรียน และปีการศึกษา</t>
+  </si>
+  <si>
+    <t>ประกอบด้วย คณะ/สถาบัน, เรื่อง, วิชา, เวลาในการสอน (นาที), ชั้นเรียน, วันที่สอน, ผู้สอน, ชั้น/กลุ่มเรียน และปีการศึกษา</t>
+  </si>
+  <si>
+    <t>ระบุระดับชั้นเรียน ปวช.1 และกลุ่มเรียน ชั้น TCT1-DERA</t>
+  </si>
+  <si>
+    <t>มีช่องระบุเวลาในการสอนเป็นหน่วย 'นาที'</t>
+  </si>
+  <si>
+    <t>ต้องระบุ โดยมีช่องสำหรับกรอกชื่อผู้สอน ชั้น/กลุ่มเรียน และปีการศึกษาอย่างชัดเจน</t>
+  </si>
+  <si>
+    <t>ระบุเป็น 'วัตถุประสงค์เชิงพฤติกรรม' (Behavioral Objectives)</t>
+  </si>
+  <si>
+    <t>มีข้อความนำระบุว่า 'หลังจบการเรียนการสอนผู้เรียนควรมีความสามารถดังนี้'</t>
+  </si>
+  <si>
+    <t>จับคู่กับคอลัมน์ 'การประเมินขั้นสำเร็จผล' เช่น การระบุข้อในใบงานหรือแบบทดสอบ</t>
+  </si>
+  <si>
+    <t>ต้องวัดผลให้ตรงตามพฤติกรรมที่ระบุในแต่ละวัตถุประสงค์เชิงพฤติกรรม โดยระบุหลักฐานการวัดผลในใบงานหรือแบบทดสอบ</t>
+  </si>
+  <si>
+    <t>ในแบบฟอร์มเริ่มต้นมีช่องกำหนดข้อ 1, 2, 3 และ 4 ไว้เป็นแนวทาง</t>
+  </si>
+  <si>
+    <t>ระบุทักษะหรือความรู้เดิมที่ผู้เรียนต้องมีก่อนเริ่มเรียนหัวข้อใหม่ เพื่อให้พร้อมต่อการรับบทเรียน</t>
+  </si>
+  <si>
+    <t>เป็นกิจกรรมหรือคำถามกระตุ้นความสนใจ เพื่อเชื่อมโยงประสบการณ์เดิมเข้าสู่เนื้อหาบทเรียนใหม่</t>
+  </si>
+  <si>
+    <t>เพื่อตรวจสอบความพร้อมของผู้เรียนและทบทวนความรู้เดิมก่อนต่อยอดไปยังเนื้อหาใหม่</t>
+  </si>
+  <si>
+    <t>มี 4 ขั้นตอนหลักตามแนวทาง MIAP ได้แก่ 1. ขั้นสนใจปัญหา (M) 2. ขั้นบอกกล่าว (I) 3. ขั้นพยายาม (A) และ 4. ขั้นสำเร็จผล (P)</t>
+  </si>
+  <si>
+    <t>ใช้ตัวย่อ '(I)' ซึ่งย่อมาจาก Information</t>
+  </si>
+  <si>
+    <t>ใช้ตัวย่อ '(A)' ซึ่งย่อมาจาก Application</t>
+  </si>
+  <si>
+    <t>ใช้ตัวย่อ '(P)' ซึ่งย่อมาจาก Progress</t>
+  </si>
+  <si>
+    <t>ตารางปฏิบัติการในแผนการสอนมีการแบ่งช่วงเวลาอย่างไร?</t>
+  </si>
+  <si>
+    <t>ตัวเลขสรุปโครงสร้างการสอนในแบบฟอร์มแสดงรหัสรูปแบบอะไร?</t>
+  </si>
+  <si>
+    <t>ในขั้นบอกกล่าว (I) มีเทคนิคการสอนย่อยอะไรให้เลือกติ๊กบ้าง?</t>
+  </si>
+  <si>
+    <t>หากครูต้องการอธิบายเนื้อหาหรือทฤษฎีในขั้นบอกกล่าว ควรเลือกช่องใด?</t>
+  </si>
+  <si>
+    <t>หากครูลงมือทำให้ดูเป็นตัวอย่างในขั้นบอกกล่าว ต้องระบุในช่องใด?</t>
+  </si>
+  <si>
+    <t>เทคนิค 'ชี้ทาง' ในขั้นบอกกล่าวคืออะไร?</t>
+  </si>
+  <si>
+    <t>เทคนิค 'สรุป' ในขั้นบอกกล่าวมีไว้เพื่ออะไร?</t>
+  </si>
+  <si>
+    <t>ในขั้นพยายาม (A) กำหนดรูปแบบกิจกรรมฝึกปฏิบัติไว้กี่รูปแบบ อะไรบ้าง?</t>
+  </si>
+  <si>
+    <t>การให้ผู้เรียนทำตามขั้นตอนที่ครูเพิ่งสาธิตไป จัดเป็นขั้นพยายามรูปแบบใด?</t>
+  </si>
+  <si>
+    <t>กิจกรรม 'แบบฝึกหัด' ในขั้นพยายามเน้นอะไร?</t>
+  </si>
+  <si>
+    <t>กิจกรรม 'แบบแก้ปัญหา' ในขั้นพยายาม เหมาะกับการเรียนการสอนแบบใด?</t>
+  </si>
+  <si>
+    <t>ตารางประเมินระดับกิจกรรมของผู้เรียนมีกี่ระดับ?</t>
+  </si>
+  <si>
+    <t>วัตถุประสงค์ของการบันทึก 'ระดับกิจกรรมผู้เรียน' ในแต่ละช่วงเวลาคืออะไร?</t>
+  </si>
+  <si>
+    <t>สิ่งสนับสนุนการเรียนการสอนในตารางมีรายการใดบ้าง?</t>
+  </si>
+  <si>
+    <t>หากใช้ PowerPoint หรือการฉายหน้าจอ ในแผนจัดอยู่ในหมวดสื่อใด?</t>
+  </si>
+  <si>
+    <t>หากมีการนำสาย LAN และคีมย้ำหัวของจริงมาใช้ จะตรงกับหมวดสื่อใด?</t>
+  </si>
+  <si>
+    <t>ถ้าครูใช้การเขียนสรุปหน้าห้อง จะจัดเป็นสื่อประเภทใดในแบบฟอร์ม?</t>
+  </si>
+  <si>
+    <t>ส่วน 'สิ่งที่แนบมาด้วย' ท้ายแผนการสอนประกอบด้วยเอกสารกี่ประเภท?</t>
+  </si>
+  <si>
+    <t>เอกสารแนบช่วยสนับสนุนการสอนของครูอย่างไร?</t>
+  </si>
+  <si>
+    <t>แบบร่างกระดาน (Board Plan) คืออะไร มีไว้เพื่อประโยชน์ใด?</t>
+  </si>
+  <si>
+    <t>มีการแบ่งช่องเวลาเป็นนาทีตั้งแต่ 1 ถึง 30 นาที และมีช่องสำหรับการบ้าน</t>
+  </si>
+  <si>
+    <t>ระบุโครงสร้างการสอนและรูปแบบการสอนที่เลือก เช่น รูปแบบ 1-2-3-4</t>
+  </si>
+  <si>
+    <t>มี 5 รูปแบบย่อย ได้แก่ บรรยาย, ถาม-ตอบ, สาธิต, ชี้ทาง และสรุป</t>
+  </si>
+  <si>
+    <t>เลือกรูปแบบ 'บรรยาย' หรือ 'ถาม-ตอบ' ตามลักษณะกิจกรรม</t>
+  </si>
+  <si>
+    <t>ระบุในช่อง 'สาธิต'</t>
+  </si>
+  <si>
+    <t>เป็นการแนะนำแนวทางหรือกระตุ้นให้ผู้เรียนค้นพบคำตอบด้วยตนเอง</t>
+  </si>
+  <si>
+    <t>ใช้สำหรับรวบยอดประเด็นสำคัญของเนื้อหาที่ได้บอกกล่าวไปให้ชัดเจนก่อนเริ่มขั้นพยายาม</t>
+  </si>
+  <si>
+    <t>มี 3 รูปแบบ ได้แก่ 1. แบบลอกเลียน 2. แบบฝึกหัด และ 3. แบบแก้ปัญหา</t>
+  </si>
+  <si>
+    <t>จัดเป็นกิจกรรม 'แบบลอกเลียน'</t>
+  </si>
+  <si>
+    <t>เน้นให้ผู้เรียนได้ฝึกฝนทบทวนและทำโจทย์เพื่อสร้างความเข้าใจที่มั่นคง</t>
+  </si>
+  <si>
+    <t>เหมาะกับโจทย์ที่มีความซับซ้อน หรือสถานการณ์จำลองที่ผู้เรียนต้องวิเคราะห์และประยุกต์ใช้ความรู้แก้ปัญหาด้วยตนเอง</t>
+  </si>
+  <si>
+    <t>แบ่งเป็น 3 ระดับ ได้แก่ ระดับสูง, ระดับปานกลาง และระดับต่ำ</t>
+  </si>
+  <si>
+    <t>เพื่อติดตามและตรวจสอบว่าผู้เรียนมีส่วนร่วม (Active Learning) มากน้อยเพียงใดตลอดแต่ละช่วงนาทีของการสอน</t>
+  </si>
+  <si>
+    <t>กระดาน, แผ่นภาพ, ใบเนื้อหา, ใบสั่งงาน, ใบทดสอบ, แผ่นใส/สไลด์, คอมพิวเตอร์, ของจริง/ตัวอย่าง และอุปกรณ์การทดลอง</t>
+  </si>
+  <si>
+    <t>จัดอยู่ในช่อง 'แผ่นใส / สไลด์' หรือ 'คอมพิวเตอร์'</t>
+  </si>
+  <si>
+    <t>ตรงกับหมวด 'ของจริง ตัวอย่าง' หรือ 'อุปกรณ์การทดลอง'</t>
+  </si>
+  <si>
+    <t>จัดอยู่ในช่อง 'กระดาน'</t>
+  </si>
+  <si>
+    <t>มี 6 ประเภท ได้แก่ แบบร่างกระดาน, ใบรายการถาม-ตอบ, ใบเนื้อหา, ใบงาน, ใบเฉลย และอื่น ๆ</t>
+  </si>
+  <si>
+    <t>ช่วยให้ครูเตรียมสื่อ เนื้อหา คำถาม-คำตอบ แบบฝึกหัด และการเขียนกระดานล่วงหน้าได้อย่างสมบูรณ์แบบและเป็นระบบ</t>
+  </si>
+  <si>
+    <t>เป็นการจำลองพื้นที่การเขียนกระดานล่วงหน้า เพื่อจัดสรรตำแหน่งหัวข้อ คำอธิบาย รูปภาพ และเฉลยให้เป็นระเบียบชัดเจน</t>
+  </si>
+  <si>
+    <t>ในแบบร่างกระดานมีการแบ่งแสดงเป็นกี่แผ่นตามตัวอย่าง?</t>
+  </si>
+  <si>
+    <t>ใบรายการถาม-ตอบ (Question &amp; Answer Sheet) ประกอบด้วยหัวข้ออะไรบ้าง?</t>
+  </si>
+  <si>
+    <t>ในใบรายการถาม-ตอบ มีการแยกการถามคำถามออกเป็นส่วนใดบ้าง?</t>
+  </si>
+  <si>
+    <t>ตัวอย่างคำถามที่ 1 ในการนำเข้าสู่บทเรียนคืออะไร?</t>
+  </si>
+  <si>
+    <t>ทำไมครูต้องเตรียมใบรายการถาม-ตอบไว้ล่วงหน้า?</t>
+  </si>
+  <si>
+    <t>ตัวอย่างมีการระบุเป็น แผ่นที่ 1/3, แผ่นที่ 2/3 และ แผ่นที่ 3/3 (รวมถึงเฉลยบนกระดาน)</t>
+  </si>
+  <si>
+    <t>ประกอบด้วย วัตถุประสงค์ (ข้อที่), รายการคำถาม และแนวคำตอบ</t>
+  </si>
+  <si>
+    <t>แยกเป็นส่วนคำถามใน 'การนำเข้าสู่บทเรียน' และคำถามที่ตรงตามแต่ละ 'วัตถุประสงค์' ของบทเรียน</t>
+  </si>
+  <si>
+    <t>คำถามคือ 'สวัสดีค่ะนักเรียน' และแนวคำตอบคือ 'สวัสดีครับ/ค่ะ'</t>
+  </si>
+  <si>
+    <t>เพื่อกำหนดทิศทางการตั้งคำถามกระตุ้นความคิด และเตรียมแนวคำตอบที่ถูกต้องไว้ตรวจสอบความเข้าใจของผู้เรียน</t>
+  </si>
+  <si>
+    <t>ใบเนื้อหาในเอกสารแนบระบุรายละเอียดหัวข้ออะไรไว้บ้าง?</t>
+  </si>
+  <si>
+    <t>ใบงานในแบบฟอร์มกำหนดโครงสร้างข้อมูลไว้อย่างไร?</t>
+  </si>
+  <si>
+    <t>ใบเฉลยในแผนการสอนคืออะไร?</t>
+  </si>
+  <si>
+    <t>ทำไมแผนการสอนจำเป็นต้องมีใบเฉลยแนบมาด้วย?</t>
+  </si>
+  <si>
+    <t>องค์ประกอบสำคัญที่ต้องมีในใบเฉลยมีอะไรบ้าง?</t>
+  </si>
+  <si>
+    <t>หากคำถามในใบงานเป็นคำถามปลายเปิด ใบเฉลยควรเขียนอย่างไร?</t>
+  </si>
+  <si>
+    <t>แหล่งข้อมูลหลักของบทเรียน (Primary Learning Resource)
+สรุปเนื้อหาที่ตรงตามจุดประสงค์เชิงพฤติกรรม โดยคัดกรองเฉพาะสาระสำคัญที่จำเป็น ไม่เยิ่นเย้อ ช่วยลดภาระการจดบันทึกของผู้เรียนและทำให้โฟกัสกับการทำความเข้าใจ
+เครื่องมือสนับสนุนการเรียนรู้ด้วยตนเอง (Self-Directed Learning)
+เปิดโอกาสให้ผู้เรียนศึกษาเนื้อหาตามจังหวะการเรียนรู้ของตนเอง (Self-paced) เหมาะกับการจัดการเรียนรู้แบบ Active Learning เช่น Flipped Classroom หรือการเรียนรู้แบบแก้ปัญหา (PBL)
+ฐานความรู้ก่อนลงมือปฏิบัติ (Theoretical Foundation)
+ในวิชาสายทักษะหรือปฏิบัติการ ใบเนื้อหาจะทำหน้าที่ปูพื้นฐานทฤษฎี คำศัพท์เฉพาะ ขั้นตอนการทำงาน และข้อควรระวัง ก่อนที่ผู้เรียนจะไปทำใบงาน (Worksheet) หรือใบปฏิบัติงาน (Job Sheet)
+สื่ออ้างอิงมาตรฐาน (Standardized Reference)
+ช่วยให้ผู้เรียนทุกคนได้รับชุดข้อมูลและมาตรฐานความรู้เดียวกัน แม้จะขาดเรียนหรือต้องการทบทวนย้อนหลัง</t>
+  </si>
+  <si>
+    <t>มีช่องระบุวิชา, ชั้น, เวลาทำ, ชื่อ-นามสกุล, รหัสประจำตัว, คำชี้แจง และรายการโจทย์ข้อคำถาม</t>
+  </si>
+  <si>
+    <t>เอกสารหรือสื่อประกอบการสอนสำหรับผู้สอน ที่ระบุคำตอบที่ถูกต้อง แสดงขั้นตอนวิธีคิด แนวทางการตอบ และเกณฑ์การให้คะแนนของใบงาน แบบฝึกหัด หรือแบบทดสอบ</t>
+  </si>
+  <si>
+    <t>เพื่อให้แผนการสอนมีความสมบูรณ์ตามมาตรฐานวิชาชีพครู ช่วยให้การประเมินผลมีความเที่ยงตรง และรองรับกรณีที่มีผู้สอนท่านอื่นนำแผนไปสอนแทนได้ทันทีโดยไม่ติดขัด</t>
+  </si>
+  <si>
+    <t>1. ส่วนหัว (ชื่อวิชา รหัสวิชา หน่วยการเรียน และอ้างอิงใบงานที่เกี่ยวข้อง)
+2. ส่วนคำตอบ/แนวคิด/ผลลัพธ์ที่คาดหวัง
+3. เกณฑ์การให้คะแนนและการกระจายคะแนนย่อย</t>
+  </si>
+  <si>
+    <t>ควรระบุเป็น "แนวคำตอบ" (Expected Key Points) โดยแจกแจงประเด็นสำคัญที่ผู้เรียนต้องตอบให้ครบ พร้อมเกณฑ์น้ำหนักคะแนนตามความลึกซึ้งของคำตอบ</t>
   </si>
 </sst>
 </file>
@@ -3514,7 +3830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3524,6 +3840,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3827,12 +4146,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C952"/>
+  <dimension ref="A1:C1001"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="75" customWidth="1"/>
+    <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="116.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -14307,6 +14626,594 @@
         <v>1077</v>
       </c>
     </row>
+    <row r="953" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A953">
+        <f>SUM(A952+1)</f>
+        <v>1001</v>
+      </c>
+      <c r="B953" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C953" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A954">
+        <f t="shared" ref="A954:A1001" si="0">SUM(A953+1)</f>
+        <v>1002</v>
+      </c>
+      <c r="B954" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C954" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A955">
+        <f t="shared" si="0"/>
+        <v>1003</v>
+      </c>
+      <c r="B955" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C955" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="956" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A956">
+        <f t="shared" si="0"/>
+        <v>1004</v>
+      </c>
+      <c r="B956" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C956" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A957">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="B957" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C957" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A958">
+        <f t="shared" si="0"/>
+        <v>1006</v>
+      </c>
+      <c r="B958" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C958" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="959" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A959">
+        <f t="shared" si="0"/>
+        <v>1007</v>
+      </c>
+      <c r="B959" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C959" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A960">
+        <f t="shared" si="0"/>
+        <v>1008</v>
+      </c>
+      <c r="B960" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C960" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A961">
+        <f t="shared" si="0"/>
+        <v>1009</v>
+      </c>
+      <c r="B961" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C961" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="962" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A962">
+        <f t="shared" si="0"/>
+        <v>1010</v>
+      </c>
+      <c r="B962" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C962" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A963">
+        <f t="shared" si="0"/>
+        <v>1011</v>
+      </c>
+      <c r="B963" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C963" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A964">
+        <f t="shared" si="0"/>
+        <v>1012</v>
+      </c>
+      <c r="B964" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C964" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="965" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A965">
+        <f t="shared" si="0"/>
+        <v>1013</v>
+      </c>
+      <c r="B965" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C965" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A966">
+        <f t="shared" si="0"/>
+        <v>1014</v>
+      </c>
+      <c r="B966" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C966" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A967">
+        <f t="shared" si="0"/>
+        <v>1015</v>
+      </c>
+      <c r="B967" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C967" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="968" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A968">
+        <f t="shared" si="0"/>
+        <v>1016</v>
+      </c>
+      <c r="B968" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C968" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A969">
+        <f t="shared" si="0"/>
+        <v>1017</v>
+      </c>
+      <c r="B969" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C969" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A970">
+        <f t="shared" si="0"/>
+        <v>1018</v>
+      </c>
+      <c r="B970" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C970" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="971" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A971">
+        <f t="shared" si="0"/>
+        <v>1019</v>
+      </c>
+      <c r="B971" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C971" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A972">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="B972" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C972" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A973">
+        <f t="shared" si="0"/>
+        <v>1021</v>
+      </c>
+      <c r="B973" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C973" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="974" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A974">
+        <f t="shared" si="0"/>
+        <v>1022</v>
+      </c>
+      <c r="B974" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C974" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A975">
+        <f t="shared" si="0"/>
+        <v>1023</v>
+      </c>
+      <c r="B975" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C975" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A976">
+        <f t="shared" si="0"/>
+        <v>1024</v>
+      </c>
+      <c r="B976" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C976" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="977" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A977">
+        <f t="shared" si="0"/>
+        <v>1025</v>
+      </c>
+      <c r="B977" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C977" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A978">
+        <f t="shared" si="0"/>
+        <v>1026</v>
+      </c>
+      <c r="B978" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C978" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A979">
+        <f t="shared" si="0"/>
+        <v>1027</v>
+      </c>
+      <c r="B979" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C979" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="980" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A980">
+        <f t="shared" si="0"/>
+        <v>1028</v>
+      </c>
+      <c r="B980" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C980" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A981">
+        <f t="shared" si="0"/>
+        <v>1029</v>
+      </c>
+      <c r="B981" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C981" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A982">
+        <f t="shared" si="0"/>
+        <v>1030</v>
+      </c>
+      <c r="B982" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C982" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="983" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A983">
+        <f t="shared" si="0"/>
+        <v>1031</v>
+      </c>
+      <c r="B983" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C983" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A984">
+        <f t="shared" si="0"/>
+        <v>1032</v>
+      </c>
+      <c r="B984" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C984" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A985">
+        <f t="shared" si="0"/>
+        <v>1033</v>
+      </c>
+      <c r="B985" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C985" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="986" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A986">
+        <f t="shared" si="0"/>
+        <v>1034</v>
+      </c>
+      <c r="B986" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C986" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A987">
+        <f t="shared" si="0"/>
+        <v>1035</v>
+      </c>
+      <c r="B987" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C987" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A988">
+        <f t="shared" si="0"/>
+        <v>1036</v>
+      </c>
+      <c r="B988" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C988" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="989" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A989">
+        <f t="shared" si="0"/>
+        <v>1037</v>
+      </c>
+      <c r="B989" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C989" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A990">
+        <f t="shared" si="0"/>
+        <v>1038</v>
+      </c>
+      <c r="B990" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C990" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A991">
+        <f t="shared" si="0"/>
+        <v>1039</v>
+      </c>
+      <c r="B991" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C991" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="992" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A992">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="B992" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C992" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A993">
+        <f t="shared" si="0"/>
+        <v>1041</v>
+      </c>
+      <c r="B993" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C993" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A994">
+        <f t="shared" si="0"/>
+        <v>1042</v>
+      </c>
+      <c r="B994" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C994" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="995" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A995">
+        <f t="shared" si="0"/>
+        <v>1043</v>
+      </c>
+      <c r="B995" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C995" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="996" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A996">
+        <f t="shared" si="0"/>
+        <v>1044</v>
+      </c>
+      <c r="B996" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C996" s="4" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A997">
+        <f t="shared" si="0"/>
+        <v>1045</v>
+      </c>
+      <c r="B997" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C997" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="998" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A998">
+        <f t="shared" si="0"/>
+        <v>1046</v>
+      </c>
+      <c r="B998" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C998" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A999">
+        <f t="shared" si="0"/>
+        <v>1047</v>
+      </c>
+      <c r="B999" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C999" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1000">
+        <f t="shared" si="0"/>
+        <v>1048</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C1000" s="4" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1001">
+        <f t="shared" si="0"/>
+        <v>1049</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>1181</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/QA_Dataset_1000_Chatbot.xlsx
+++ b/QA_Dataset_1000_Chatbot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\doc-sheet-chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD949DC9-6330-4138-A081-E4B71E99F579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FCA06-7BA6-4B7D-9B5A-D46AE0883C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4176,7 +4176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -4539,7 +4539,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -4616,7 +4616,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -5210,7 +5210,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="132" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -5221,7 +5221,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>174</v>
       </c>
@@ -6079,7 +6079,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>178</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>180</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>182</v>
       </c>
@@ -6167,7 +6167,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>184</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>194</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>198</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>200</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>210</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>212</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>214</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>216</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>218</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>220</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>222</v>
       </c>
@@ -6607,7 +6607,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>226</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>227</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>228</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>229</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>230</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -6706,7 +6706,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>232</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>234</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>236</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>238</v>
       </c>
@@ -6783,7 +6783,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>240</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -6816,7 +6816,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>242</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>244</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>246</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -6882,7 +6882,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>248</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
         <v>265</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A267" s="2">
         <v>266</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A268" s="2">
         <v>267</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A269" s="2">
         <v>268</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A270" s="2">
         <v>269</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A271" s="2">
         <v>270</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A272" s="2">
         <v>271</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A273" s="2">
         <v>272</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>273</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>274</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>275</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>276</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>277</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>278</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>279</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A281" s="2">
         <v>280</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A282" s="2">
         <v>281</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A283" s="2">
         <v>282</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A284" s="2">
         <v>283</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A285" s="2">
         <v>284</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A286" s="2">
         <v>285</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
         <v>286</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A288" s="2">
         <v>287</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A289" s="2">
         <v>288</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A290" s="2">
         <v>289</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A291" s="2">
         <v>290</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A292" s="2">
         <v>291</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A293" s="2">
         <v>292</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A294" s="2">
         <v>293</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A295" s="2">
         <v>294</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>295</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>296</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A299" s="2">
         <v>298</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>299</v>
       </c>
@@ -7454,7 +7454,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>300</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A302" s="2">
         <v>301</v>
       </c>
@@ -7476,7 +7476,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A303" s="2">
         <v>302</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A304" s="2">
         <v>303</v>
       </c>
@@ -7498,7 +7498,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>304</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>305</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>306</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
         <v>307</v>
       </c>
@@ -7542,7 +7542,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>308</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>309</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>310</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>311</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>312</v>
       </c>
@@ -7597,7 +7597,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>313</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>314</v>
       </c>
@@ -7619,7 +7619,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>315</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>316</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>317</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>318</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>319</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="132" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>320</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>321</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>322</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>323</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>324</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>325</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>326</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>327</v>
       </c>
@@ -7762,7 +7762,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>328</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>329</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>330</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>331</v>
       </c>
@@ -7806,7 +7806,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>332</v>
       </c>
@@ -7817,7 +7817,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>333</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A335" s="2">
         <v>334</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A336" s="2">
         <v>335</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>336</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A338" s="2">
         <v>337</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A339" s="2">
         <v>338</v>
       </c>
@@ -7883,7 +7883,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A340" s="2">
         <v>339</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A341" s="2">
         <v>340</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A342" s="2">
         <v>341</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A343" s="2">
         <v>342</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A344" s="2">
         <v>343</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A345" s="2">
         <v>344</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A346" s="2">
         <v>345</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="347" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A347" s="2">
         <v>346</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>347</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A349" s="2">
         <v>348</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A350" s="2">
         <v>349</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A351" s="2">
         <v>350</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A352" s="2">
         <v>351</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A353" s="2">
         <v>352</v>
       </c>
@@ -8037,7 +8037,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A354" s="2">
         <v>353</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A355" s="2">
         <v>354</v>
       </c>
@@ -8059,7 +8059,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A356" s="2">
         <v>355</v>
       </c>
@@ -8070,7 +8070,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A357" s="2">
         <v>356</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A358" s="2">
         <v>357</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A359" s="2">
         <v>358</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A360" s="2">
         <v>359</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A361" s="2">
         <v>360</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A362" s="2">
         <v>361</v>
       </c>
@@ -8136,7 +8136,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A363" s="2">
         <v>362</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A364" s="2">
         <v>363</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A365" s="2">
         <v>364</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
         <v>365</v>
       </c>
@@ -8180,7 +8180,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
         <v>366</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
         <v>367</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
         <v>368</v>
       </c>
@@ -8213,7 +8213,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
         <v>369</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
         <v>370</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A372" s="2">
         <v>371</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A373" s="2">
         <v>372</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A374" s="2">
         <v>373</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A375" s="2">
         <v>374</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A376" s="2">
         <v>375</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
         <v>376</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
         <v>377</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A379" s="2">
         <v>378</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A380" s="2">
         <v>379</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A381" s="2">
         <v>380</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A382" s="2">
         <v>381</v>
       </c>
@@ -8356,7 +8356,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A383" s="2">
         <v>382</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A384" s="2">
         <v>383</v>
       </c>
@@ -8378,7 +8378,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A385" s="2">
         <v>384</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A386" s="2">
         <v>392</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A387" s="2">
         <v>393</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A388" s="2">
         <v>394</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A389" s="2">
         <v>395</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A390" s="2">
         <v>396</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A391" s="2">
         <v>397</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A392" s="2">
         <v>398</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A393" s="2">
         <v>399</v>
       </c>
@@ -8477,7 +8477,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A394" s="2">
         <v>400</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
         <v>401</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A396" s="2">
         <v>402</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A397" s="2">
         <v>403</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A398" s="2">
         <v>404</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A399" s="2">
         <v>405</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A408" s="2">
         <v>414</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A409" s="2">
         <v>415</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A410" s="2">
         <v>416</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A411" s="2">
         <v>417</v>
       </c>
@@ -8675,7 +8675,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A412" s="2">
         <v>418</v>
       </c>
@@ -8686,7 +8686,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A413" s="2">
         <v>419</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" s="2">
         <v>420</v>
       </c>
@@ -8708,7 +8708,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="415" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A415" s="2">
         <v>421</v>
       </c>
@@ -8730,7 +8730,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A417" s="2">
         <v>423</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="418" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A418" s="2">
         <v>424</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A420" s="2">
         <v>426</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="422" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A422" s="2">
         <v>428</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="427" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A427" s="2">
         <v>433</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="435" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A435" s="2">
         <v>441</v>
       </c>
@@ -8939,7 +8939,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="436" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A436" s="2">
         <v>442</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A437" s="2">
         <v>443</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A438" s="2">
         <v>444</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A439" s="2">
         <v>445</v>
       </c>
@@ -8983,7 +8983,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A440" s="2">
         <v>446</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="441" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A441" s="2">
         <v>447</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A442" s="2">
         <v>448</v>
       </c>
@@ -9016,7 +9016,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="443" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A443" s="2">
         <v>449</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="444" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A444" s="2">
         <v>450</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="445" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A445" s="2">
         <v>451</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="446" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A446" s="2">
         <v>452</v>
       </c>
@@ -9060,7 +9060,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="447" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A447" s="2">
         <v>453</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A448" s="2">
         <v>454</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="449" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A449" s="2">
         <v>455</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="450" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A450" s="2">
         <v>456</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="451" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A451" s="2">
         <v>457</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A452" s="2">
         <v>458</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A453" s="2">
         <v>459</v>
       </c>
@@ -9137,7 +9137,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="454" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A454" s="2">
         <v>460</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="455" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A455" s="2">
         <v>461</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="456" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A456" s="2">
         <v>462</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="457" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A457" s="2">
         <v>463</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="458" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A458" s="2">
         <v>464</v>
       </c>
@@ -9192,7 +9192,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="459" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A459" s="2">
         <v>465</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="460" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A460" s="2">
         <v>466</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="461" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A461" s="2">
         <v>467</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="462" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A462" s="2">
         <v>468</v>
       </c>
@@ -9236,7 +9236,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="463" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A463" s="2">
         <v>469</v>
       </c>
@@ -9247,7 +9247,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="464" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A464" s="2">
         <v>470</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="465" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A465" s="2">
         <v>471</v>
       </c>
@@ -9269,7 +9269,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="466" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A466" s="2">
         <v>472</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="467" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A467" s="2">
         <v>473</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="468" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A468" s="2">
         <v>474</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="469" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A469" s="2">
         <v>475</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="470" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A470" s="2">
         <v>476</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="471" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A471" s="2">
         <v>477</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="472" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A472" s="2">
         <v>478</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A473" s="2">
         <v>479</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="474" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A474" s="2">
         <v>480</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="475" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A475" s="2">
         <v>481</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="476" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A476" s="2">
         <v>482</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="477" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A477" s="2">
         <v>483</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="478" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A478" s="2">
         <v>484</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="479" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A479" s="2">
         <v>485</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="480" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A480" s="2">
         <v>486</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="481" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A481" s="2">
         <v>487</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="482" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A482" s="2">
         <v>488</v>
       </c>
@@ -9456,7 +9456,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="483" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A483" s="2">
         <v>489</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="484" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A484" s="2">
         <v>490</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="485" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A485" s="2">
         <v>491</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="486" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A486" s="2">
         <v>492</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="487" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A487" s="2">
         <v>493</v>
       </c>
@@ -9511,7 +9511,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="488" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A488" s="2">
         <v>494</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="489" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A489" s="2">
         <v>495</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="490" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A490" s="2">
         <v>496</v>
       </c>
@@ -9544,7 +9544,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="491" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A491" s="2">
         <v>497</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="492" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A492" s="2">
         <v>498</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="493" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A493" s="2">
         <v>499</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="494" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A494" s="2">
         <v>500</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="495" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A495" s="2">
         <v>501</v>
       </c>
@@ -9599,7 +9599,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="496" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A496" s="2">
         <v>502</v>
       </c>
@@ -9610,7 +9610,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="497" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A497" s="2">
         <v>503</v>
       </c>
@@ -9621,7 +9621,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="498" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A498" s="2">
         <v>504</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="499" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A499" s="2">
         <v>505</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="500" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A500" s="2">
         <v>506</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="501" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A501" s="2">
         <v>507</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="502" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A502" s="2">
         <v>508</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="503" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A503" s="2">
         <v>509</v>
       </c>
@@ -9687,7 +9687,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="504" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A504" s="2">
         <v>510</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="505" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A505" s="2">
         <v>511</v>
       </c>
@@ -9709,7 +9709,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="506" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A506" s="2">
         <v>512</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="507" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A507" s="2">
         <v>513</v>
       </c>
@@ -9731,7 +9731,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="508" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A508" s="2">
         <v>514</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="509" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A509" s="2">
         <v>515</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="510" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A510" s="2">
         <v>516</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="511" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A511" s="2">
         <v>517</v>
       </c>
@@ -9775,7 +9775,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="512" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A512" s="2">
         <v>518</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="513" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A513" s="2">
         <v>519</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="514" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A514" s="2">
         <v>520</v>
       </c>
@@ -9808,7 +9808,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="515" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A515" s="2">
         <v>521</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="516" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A516" s="2">
         <v>522</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="517" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A517" s="2">
         <v>523</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="518" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A518" s="2">
         <v>524</v>
       </c>
@@ -9852,7 +9852,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="519" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A519" s="2">
         <v>525</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="520" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A520" s="2">
         <v>526</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="521" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A521" s="2">
         <v>527</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="522" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A522" s="2">
         <v>528</v>
       </c>
@@ -9896,7 +9896,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="523" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A523" s="2">
         <v>529</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="524" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A524" s="2">
         <v>530</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="525" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A525" s="2">
         <v>531</v>
       </c>
@@ -9929,7 +9929,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="526" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A526" s="2">
         <v>532</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="527" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A527" s="2">
         <v>533</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="528" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A528" s="2">
         <v>534</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="529" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A529" s="2">
         <v>535</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="530" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A530" s="2">
         <v>536</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="531" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A531" s="2">
         <v>537</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="532" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A532" s="2">
         <v>538</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="533" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A533" s="2">
         <v>539</v>
       </c>
@@ -10017,7 +10017,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="534" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A534" s="2">
         <v>540</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="535" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A535" s="2">
         <v>541</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="536" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A536" s="2">
         <v>542</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="537" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A537" s="2">
         <v>543</v>
       </c>
@@ -10061,7 +10061,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="538" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A538" s="2">
         <v>544</v>
       </c>
@@ -10072,7 +10072,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="539" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A539" s="2">
         <v>545</v>
       </c>
@@ -10083,7 +10083,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="540" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A540" s="2">
         <v>546</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="541" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A541" s="2">
         <v>547</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="542" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A542" s="2">
         <v>548</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="543" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A543" s="2">
         <v>549</v>
       </c>
@@ -10127,7 +10127,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="544" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A544" s="2">
         <v>550</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="545" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A545" s="2">
         <v>551</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="546" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A546" s="2">
         <v>552</v>
       </c>
@@ -10160,7 +10160,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="547" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A547" s="2">
         <v>553</v>
       </c>
@@ -10171,7 +10171,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="548" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A548" s="2">
         <v>554</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="549" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A549" s="2">
         <v>555</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="550" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A550" s="2">
         <v>556</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="551" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A551" s="2">
         <v>557</v>
       </c>
@@ -10215,7 +10215,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="552" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A552" s="2">
         <v>558</v>
       </c>
@@ -10226,7 +10226,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="553" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A553" s="2">
         <v>559</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="554" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A554" s="2">
         <v>560</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="555" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A555" s="2">
         <v>561</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="556" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A556" s="2">
         <v>562</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="557" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A557" s="2">
         <v>563</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="558" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A558" s="2">
         <v>564</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="559" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A559" s="2">
         <v>565</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="560" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A560" s="2">
         <v>566</v>
       </c>
@@ -10314,7 +10314,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="561" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A561" s="2">
         <v>567</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="562" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A562" s="2">
         <v>568</v>
       </c>
@@ -10347,7 +10347,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="564" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A564" s="2">
         <v>570</v>
       </c>
@@ -10358,7 +10358,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="565" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A565" s="2">
         <v>571</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="566" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A566" s="2">
         <v>572</v>
       </c>
@@ -10380,7 +10380,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="567" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A567" s="2">
         <v>573</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="570" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A570" s="2">
         <v>576</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="571" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A571" s="2">
         <v>577</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="572" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A572" s="2">
         <v>578</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="573" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A573" s="2">
         <v>579</v>
       </c>
@@ -10457,7 +10457,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="574" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A574" s="2">
         <v>580</v>
       </c>
@@ -10468,7 +10468,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="575" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A575" s="2">
         <v>581</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="577" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A577" s="2">
         <v>583</v>
       </c>
@@ -10501,7 +10501,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="578" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A578" s="2">
         <v>584</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="579" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A579" s="2">
         <v>585</v>
       </c>
@@ -10523,7 +10523,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="580" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A580" s="2">
         <v>586</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="581" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A581" s="2">
         <v>587</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="582" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A582" s="2">
         <v>588</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="583" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A583" s="2">
         <v>589</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="584" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A584" s="2">
         <v>590</v>
       </c>
@@ -10578,7 +10578,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="585" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A585" s="2">
         <v>591</v>
       </c>
@@ -10589,7 +10589,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="586" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A586" s="2">
         <v>592</v>
       </c>
@@ -10600,7 +10600,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="587" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A587" s="2">
         <v>593</v>
       </c>
@@ -10611,7 +10611,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="588" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A588" s="2">
         <v>594</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="589" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" s="2">
         <v>595</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="590" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" s="2">
         <v>596</v>
       </c>
@@ -10655,7 +10655,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="592" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A592" s="2">
         <v>598</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="599" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A599" s="2">
         <v>605</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="603" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A603" s="2">
         <v>609</v>
       </c>
@@ -10787,7 +10787,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="604" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A604" s="2">
         <v>610</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="605" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A605" s="2">
         <v>611</v>
       </c>
@@ -10809,7 +10809,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="606" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A606" s="2">
         <v>612</v>
       </c>
@@ -10820,7 +10820,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="607" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A607" s="2">
         <v>613</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="608" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A608" s="2">
         <v>614</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="609" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A609" s="2">
         <v>615</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="611" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A611" s="2">
         <v>617</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="612" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A612" s="2">
         <v>618</v>
       </c>
@@ -10886,7 +10886,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="613" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A613" s="2">
         <v>619</v>
       </c>
@@ -10897,7 +10897,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="614" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A614" s="2">
         <v>620</v>
       </c>
@@ -10908,7 +10908,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="615" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A615" s="2">
         <v>621</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="616" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A616" s="2">
         <v>622</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="617" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A617" s="2">
         <v>623</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="618" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A618" s="2">
         <v>624</v>
       </c>
@@ -10963,7 +10963,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="620" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A620" s="2">
         <v>626</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="621" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A621" s="2">
         <v>627</v>
       </c>
@@ -10985,7 +10985,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="622" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A622" s="2">
         <v>628</v>
       </c>
@@ -10996,7 +10996,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="623" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A623" s="2">
         <v>629</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="624" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" s="2">
         <v>630</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="630" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A630" s="2">
         <v>636</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="631" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" s="2">
         <v>637</v>
       </c>
@@ -11161,7 +11161,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="638" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A638" s="2">
         <v>644</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="639" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A639" s="2">
         <v>645</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="640" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A640" s="2">
         <v>646</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="641" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A641" s="2">
         <v>647</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="642" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A642" s="2">
         <v>648</v>
       </c>
@@ -11216,7 +11216,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="643" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A643" s="2">
         <v>649</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="644" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A644" s="2">
         <v>650</v>
       </c>
@@ -11238,7 +11238,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="645" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A645" s="2">
         <v>651</v>
       </c>
@@ -11249,7 +11249,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="646" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A646" s="2">
         <v>652</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="647" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A647" s="2">
         <v>653</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="648" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A648" s="2">
         <v>654</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="649" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A649" s="2">
         <v>655</v>
       </c>
@@ -11293,7 +11293,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="650" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A650" s="2">
         <v>656</v>
       </c>
@@ -11304,7 +11304,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="651" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A651" s="2">
         <v>657</v>
       </c>
@@ -11326,7 +11326,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="653" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A653" s="2">
         <v>659</v>
       </c>
@@ -11337,7 +11337,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="654" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A654" s="2">
         <v>660</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="655" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A655" s="2">
         <v>661</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="656" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A656" s="2">
         <v>662</v>
       </c>
@@ -11370,7 +11370,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="657" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A657" s="2">
         <v>663</v>
       </c>
@@ -11381,7 +11381,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="658" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A658" s="2">
         <v>664</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="660" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A660" s="2">
         <v>666</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="661" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A661" s="2">
         <v>667</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="662" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A662" s="2">
         <v>668</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="663" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A663" s="2">
         <v>669</v>
       </c>
@@ -11447,7 +11447,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="664" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A664" s="2">
         <v>670</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="665" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A665" s="2">
         <v>671</v>
       </c>
@@ -11546,7 +11546,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="673" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A673" s="2">
         <v>679</v>
       </c>
@@ -11557,7 +11557,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="674" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A674" s="2">
         <v>680</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="675" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A675" s="2">
         <v>681</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="676" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A676" s="2">
         <v>682</v>
       </c>
@@ -11590,7 +11590,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="677" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A677" s="2">
         <v>683</v>
       </c>
@@ -11601,7 +11601,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="678" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A678" s="2">
         <v>684</v>
       </c>
@@ -11612,7 +11612,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="679" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A679" s="2">
         <v>685</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="687" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A687" s="2">
         <v>693</v>
       </c>
@@ -11711,7 +11711,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="688" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A688" s="2">
         <v>694</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="689" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A689" s="2">
         <v>695</v>
       </c>
@@ -11733,7 +11733,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="690" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A690" s="2">
         <v>696</v>
       </c>
@@ -11744,7 +11744,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="691" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A691" s="2">
         <v>697</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="692" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A692" s="2">
         <v>698</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="693" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A693" s="2">
         <v>699</v>
       </c>
@@ -11777,7 +11777,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="694" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A694" s="2">
         <v>700</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="697" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A697" s="2">
         <v>703</v>
       </c>
@@ -11821,7 +11821,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="698" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A698" s="2">
         <v>704</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="702" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A702" s="2">
         <v>708</v>
       </c>
@@ -11876,7 +11876,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="703" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A703" s="2">
         <v>709</v>
       </c>
@@ -11887,7 +11887,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="704" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A704" s="2">
         <v>710</v>
       </c>
@@ -11898,7 +11898,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="705" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A705" s="2">
         <v>711</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="706" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A706" s="2">
         <v>712</v>
       </c>
@@ -11920,7 +11920,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="707" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A707" s="2">
         <v>713</v>
       </c>
@@ -11931,7 +11931,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="708" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A708" s="2">
         <v>756</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="709" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A709" s="2">
         <v>757</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="710" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A710" s="2">
         <v>758</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="711" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A711" s="2">
         <v>759</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="712" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A712" s="2">
         <v>760</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="713" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A713" s="2">
         <v>761</v>
       </c>
@@ -11997,7 +11997,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="714" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:3" ht="66" x14ac:dyDescent="0.3">
       <c r="A714" s="2">
         <v>762</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="715" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A715" s="2">
         <v>763</v>
       </c>
@@ -12019,7 +12019,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="716" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A716" s="2">
         <v>764</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="717" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A717" s="2">
         <v>765</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="718" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A718" s="2">
         <v>766</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="719" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A719" s="2">
         <v>767</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="720" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A720" s="2">
         <v>768</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="721" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A721" s="2">
         <v>769</v>
       </c>
@@ -12162,7 +12162,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="729" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A729" s="2">
         <v>777</v>
       </c>
@@ -12173,7 +12173,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="730" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A730" s="2">
         <v>778</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="731" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A731" s="2">
         <v>779</v>
       </c>
@@ -12195,7 +12195,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="732" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A732" s="2">
         <v>780</v>
       </c>
@@ -12206,7 +12206,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="733" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A733" s="2">
         <v>781</v>
       </c>
@@ -12217,7 +12217,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="734" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A734" s="2">
         <v>782</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="735" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A735" s="2">
         <v>783</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="736" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A736" s="2">
         <v>784</v>
       </c>
@@ -12250,7 +12250,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="737" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A737" s="2">
         <v>785</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="738" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A738" s="2">
         <v>786</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="739" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A739" s="2">
         <v>787</v>
       </c>
@@ -12283,7 +12283,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="740" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A740" s="2">
         <v>788</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="741" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A741" s="2">
         <v>789</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="742" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A742" s="2">
         <v>790</v>
       </c>
@@ -12316,7 +12316,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="743" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A743" s="2">
         <v>791</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="744" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A744" s="2">
         <v>792</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="745" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A745" s="2">
         <v>793</v>
       </c>
@@ -12349,7 +12349,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="746" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A746" s="2">
         <v>794</v>
       </c>
@@ -12360,7 +12360,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="747" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A747" s="2">
         <v>795</v>
       </c>
@@ -12371,7 +12371,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="748" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A748" s="2">
         <v>796</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="749" spans="1:3" ht="66" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A749" s="2">
         <v>797</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="750" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A750" s="2">
         <v>798</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="751" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A751" s="2">
         <v>799</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="752" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A752" s="2">
         <v>800</v>
       </c>
@@ -12426,7 +12426,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="753" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A753" s="2">
         <v>801</v>
       </c>
@@ -12437,7 +12437,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="754" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A754" s="2">
         <v>802</v>
       </c>
@@ -12448,7 +12448,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="755" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A755" s="2">
         <v>803</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="756" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A756" s="2">
         <v>804</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="757" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A757" s="2">
         <v>805</v>
       </c>
@@ -12481,7 +12481,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="758" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A758" s="2">
         <v>806</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="759" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A759" s="2">
         <v>807</v>
       </c>
@@ -12503,7 +12503,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="760" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A760" s="2">
         <v>808</v>
       </c>
@@ -12514,7 +12514,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="761" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A761" s="2">
         <v>809</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="762" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A762" s="2">
         <v>810</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="763" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A763" s="2">
         <v>811</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="771" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A771" s="2">
         <v>819</v>
       </c>
@@ -12635,7 +12635,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="772" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A772" s="2">
         <v>820</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="773" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A773" s="2">
         <v>821</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="774" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A774" s="2">
         <v>822</v>
       </c>
@@ -12668,7 +12668,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="775" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A775" s="2">
         <v>823</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="776" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A776" s="2">
         <v>824</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="777" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A777" s="2">
         <v>825</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="780" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A780" s="2">
         <v>828</v>
       </c>
@@ -12866,7 +12866,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="793" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A793" s="2">
         <v>841</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="794" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A794" s="2">
         <v>842</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="795" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A795" s="2">
         <v>843</v>
       </c>
@@ -12910,7 +12910,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="797" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A797" s="2">
         <v>845</v>
       </c>
@@ -12932,7 +12932,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="799" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A799" s="2">
         <v>847</v>
       </c>
@@ -12943,7 +12943,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="800" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A800" s="2">
         <v>848</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="801" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A801" s="2">
         <v>849</v>
       </c>
@@ -12965,7 +12965,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="802" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A802" s="2">
         <v>850</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="803" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A803" s="2">
         <v>851</v>
       </c>
@@ -12987,7 +12987,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="804" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A804" s="2">
         <v>852</v>
       </c>
@@ -12998,7 +12998,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="805" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A805" s="2">
         <v>853</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="827" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A827" s="2">
         <v>875</v>
       </c>
@@ -13251,7 +13251,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="828" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A828" s="2">
         <v>876</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="829" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A829" s="2">
         <v>877</v>
       </c>
@@ -13273,7 +13273,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="830" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A830" s="2">
         <v>878</v>
       </c>
@@ -13284,7 +13284,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="831" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A831" s="2">
         <v>879</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="832" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A832" s="2">
         <v>880</v>
       </c>
@@ -13306,7 +13306,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="833" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A833" s="2">
         <v>881</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="834" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A834" s="2">
         <v>882</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="835" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A835" s="2">
         <v>883</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="836" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A836" s="2">
         <v>884</v>
       </c>
@@ -13350,7 +13350,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="837" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A837" s="2">
         <v>885</v>
       </c>
@@ -13361,7 +13361,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="838" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A838" s="2">
         <v>886</v>
       </c>
@@ -13372,7 +13372,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="839" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A839" s="2">
         <v>887</v>
       </c>
@@ -13383,7 +13383,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="840" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A840" s="2">
         <v>888</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="841" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A841" s="2">
         <v>889</v>
       </c>
@@ -13405,7 +13405,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="842" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A842" s="2">
         <v>890</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="843" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A843" s="2">
         <v>891</v>
       </c>
@@ -13427,7 +13427,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="844" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A844" s="2">
         <v>892</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="845" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A845" s="2">
         <v>893</v>
       </c>
@@ -13449,7 +13449,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="846" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A846" s="2">
         <v>894</v>
       </c>
@@ -13460,7 +13460,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="847" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A847" s="2">
         <v>895</v>
       </c>
@@ -13471,7 +13471,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="848" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A848" s="2">
         <v>896</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="849" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A849" s="2">
         <v>897</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="850" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A850" s="2">
         <v>898</v>
       </c>
@@ -13504,7 +13504,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="851" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A851" s="2">
         <v>899</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="852" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A852" s="2">
         <v>900</v>
       </c>
@@ -13526,7 +13526,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="853" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A853" s="2">
         <v>901</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="854" spans="1:3" ht="92.4" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:3" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A854" s="2">
         <v>902</v>
       </c>
@@ -13548,7 +13548,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="855" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A855" s="2">
         <v>903</v>
       </c>
@@ -13559,7 +13559,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="856" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A856" s="2">
         <v>904</v>
       </c>
@@ -13570,7 +13570,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="857" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A857" s="2">
         <v>905</v>
       </c>
@@ -13581,7 +13581,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="858" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A858" s="2">
         <v>906</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="859" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A859" s="2">
         <v>907</v>
       </c>
@@ -13603,7 +13603,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="860" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A860" s="2">
         <v>908</v>
       </c>
@@ -13614,7 +13614,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="861" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A861" s="2">
         <v>909</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="862" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A862" s="2">
         <v>910</v>
       </c>
@@ -13636,7 +13636,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="863" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A863" s="2">
         <v>911</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="864" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A864" s="2">
         <v>912</v>
       </c>
@@ -13658,7 +13658,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="865" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A865" s="2">
         <v>913</v>
       </c>
@@ -13669,7 +13669,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="866" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A866" s="2">
         <v>914</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="867" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A867" s="2">
         <v>915</v>
       </c>
@@ -13691,7 +13691,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="868" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A868" s="2">
         <v>916</v>
       </c>
@@ -13801,7 +13801,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="878" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A878" s="2">
         <v>926</v>
       </c>
@@ -13834,7 +13834,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="881" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A881" s="2">
         <v>929</v>
       </c>
@@ -13845,7 +13845,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="882" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A882" s="2">
         <v>930</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="884" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A884" s="2">
         <v>932</v>
       </c>
@@ -13900,7 +13900,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="887" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A887" s="2">
         <v>935</v>
       </c>
@@ -13922,7 +13922,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="889" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A889" s="2">
         <v>937</v>
       </c>
@@ -14010,7 +14010,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="897" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A897" s="2">
         <v>945</v>
       </c>
@@ -14021,7 +14021,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="898" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A898" s="2">
         <v>946</v>
       </c>
@@ -14032,7 +14032,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="899" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A899" s="2">
         <v>947</v>
       </c>
@@ -14043,7 +14043,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="900" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A900" s="2">
         <v>948</v>
       </c>
@@ -14054,7 +14054,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="901" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A901" s="2">
         <v>949</v>
       </c>
@@ -14065,7 +14065,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="902" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A902" s="2">
         <v>950</v>
       </c>
@@ -14076,7 +14076,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="903" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A903" s="2">
         <v>951</v>
       </c>
@@ -14087,7 +14087,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="904" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A904" s="2">
         <v>952</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="905" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A905" s="2">
         <v>953</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="906" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A906" s="2">
         <v>954</v>
       </c>
@@ -14120,7 +14120,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="907" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A907" s="2">
         <v>955</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="908" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A908" s="2">
         <v>956</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="909" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A909" s="2">
         <v>957</v>
       </c>
@@ -14153,7 +14153,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="910" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A910" s="2">
         <v>958</v>
       </c>
@@ -14241,7 +14241,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="918" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A918" s="2">
         <v>966</v>
       </c>
@@ -14252,7 +14252,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="919" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A919" s="2">
         <v>967</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="920" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A920" s="2">
         <v>968</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="921" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A921" s="2">
         <v>969</v>
       </c>
@@ -14285,7 +14285,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="922" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A922" s="2">
         <v>970</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="923" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A923" s="2">
         <v>971</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="924" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A924" s="2">
         <v>972</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="926" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A926" s="2">
         <v>974</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="932" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A932" s="2">
         <v>980</v>
       </c>
@@ -14406,7 +14406,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="933" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A933" s="2">
         <v>981</v>
       </c>
@@ -14417,7 +14417,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="934" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A934" s="2">
         <v>982</v>
       </c>
@@ -14428,7 +14428,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="935" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A935" s="2">
         <v>983</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="936" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A936" s="2">
         <v>984</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="937" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A937" s="2">
         <v>985</v>
       </c>
@@ -14461,7 +14461,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="938" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="938" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A938" s="2">
         <v>986</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="939" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A939" s="2">
         <v>987</v>
       </c>
@@ -14483,7 +14483,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="940" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A940" s="2">
         <v>988</v>
       </c>
@@ -14494,7 +14494,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="941" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A941" s="2">
         <v>989</v>
       </c>
@@ -14505,7 +14505,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="942" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A942" s="2">
         <v>990</v>
       </c>
@@ -14516,7 +14516,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="943" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A943" s="2">
         <v>991</v>
       </c>
@@ -14527,7 +14527,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="944" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="944" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A944" s="2">
         <v>992</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="945" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="945" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A945" s="2">
         <v>993</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="946" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A946" s="2">
         <v>994</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="947" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A947" s="2">
         <v>995</v>
       </c>
@@ -14571,7 +14571,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="948" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="948" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A948" s="2">
         <v>996</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="949" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A949" s="2">
         <v>997</v>
       </c>
@@ -14593,7 +14593,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="950" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A950" s="2">
         <v>998</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="951" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="951" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A951" s="2">
         <v>999</v>
       </c>
@@ -14615,7 +14615,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="952" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A952" s="2">
         <v>1000</v>
       </c>

--- a/QA_Dataset_1000_Chatbot.xlsx
+++ b/QA_Dataset_1000_Chatbot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\doc-sheet-chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29FCA06-7BA6-4B7D-9B5A-D46AE0883C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2291720-DB9E-4C75-BE23-F9B7FDADB272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="1184">
   <si>
     <t>ลำดับข้อ</t>
   </si>
@@ -3744,6 +3744,12 @@
   </si>
   <si>
     <t>ควรระบุเป็น "แนวคำตอบ" (Expected Key Points) โดยแจกแจงประเด็นสำคัญที่ผู้เรียนต้องตอบให้ครบ พร้อมเกณฑ์น้ำหนักคะแนนตามความลึกซึ้งของคำตอบ</t>
+  </si>
+  <si>
+    <t>ใบเฉลยคืออะไร</t>
+  </si>
+  <si>
+    <t>ใบเฉลย (Answer Key / Solution Sheet) คือ เอกสารหรือสื่อที่รวบรวมคำตอบที่ถูกต้อง พร้อมแนวทางการตอบหรือวิธีทำของแบบทดสอบ แบบฝึกหัด หรือใบงาน โดยจัดทำขึ้นเพื่อใช้เป็นเกณฑ์มาตรฐานในการตรวจและประเมินผลการเรียนรู้</t>
   </si>
 </sst>
 </file>
@@ -4146,12 +4152,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1001"/>
+  <dimension ref="A1:C1002"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="71.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="116.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="193.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -15214,6 +15220,17 @@
         <v>1181</v>
       </c>
     </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1002">
+        <v>1050</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C1002" t="s">
+        <v>1183</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/QA_Dataset_1000_Chatbot.xlsx
+++ b/QA_Dataset_1000_Chatbot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\doc-sheet-chatbot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2291720-DB9E-4C75-BE23-F9B7FDADB272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388E0724-5649-44BA-8979-2B7EA05D3F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="1193">
   <si>
     <t>ลำดับข้อ</t>
   </si>
@@ -3751,12 +3751,39 @@
   <si>
     <t>ใบเฉลย (Answer Key / Solution Sheet) คือ เอกสารหรือสื่อที่รวบรวมคำตอบที่ถูกต้อง พร้อมแนวทางการตอบหรือวิธีทำของแบบทดสอบ แบบฝึกหัด หรือใบงาน โดยจัดทำขึ้นเพื่อใช้เป็นเกณฑ์มาตรฐานในการตรวจและประเมินผลการเรียนรู้</t>
   </si>
+  <si>
+    <t>M ใน MIAP คืออะไร</t>
+  </si>
+  <si>
+    <t>M ในรูปแบบการสอน MIAP ย่อมาจาก Motivation (ขั้นสนใจปัญหา / ขั้นเร้าความสนใจ)</t>
+  </si>
+  <si>
+    <t>I ใน MIAP คืออะไร</t>
+  </si>
+  <si>
+    <t>I ในรูปแบบการสอน MIAP ย่อมาจาก Information (ขั้นศึกษาข้อมูล / ขั้นให้เนื้อหาความรู้)</t>
+  </si>
+  <si>
+    <t>A ใน MIAP คืออะไร</t>
+  </si>
+  <si>
+    <t>A ในรูปแบบการสอน MIAP ย่อมาจาก Application (ขั้นพยายาม / ขั้นนำไปใช้และลงมือปฏิบัติ)</t>
+  </si>
+  <si>
+    <t>P ในรูปแบบการสอน MIAP ย่อมาจาก Progress (ขั้นสำเร็จผล / ขั้นประเมินผลความก้าวหน้า)</t>
+  </si>
+  <si>
+    <t>MIAP คืออะไร</t>
+  </si>
+  <si>
+    <t>MIAP คือ รูปแบบหรือกระบวนการจัดกิจกรรมการเรียนรู้ 4 ขั้นตอนที่นิยมใช้อย่างแพร่หลายในการเรียนการสอนสายอาชีวศึกษา เทคนิค และครุศาสตร์อุตสาหกรรม โดยเน้นให้ผู้เรียนเปลี่ยนผ่านจาก "ความเข้าใจในทฤษฎี" ไปสู่ "การลงมือปฏิบัติได้จริงอย่างถูกต้องและปลอดภัย"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3778,6 +3805,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3836,7 +3868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3850,6 +3882,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4152,7 +4185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1002"/>
+  <dimension ref="A1:C1007"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4611,7 +4644,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5755,7 +5788,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -5766,7 +5799,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -5777,7 +5810,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -5788,7 +5821,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -5799,7 +5832,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -5810,7 +5843,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -5821,7 +5854,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -5832,7 +5865,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -5843,7 +5876,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -5854,7 +5887,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -5865,7 +5898,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -5876,7 +5909,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -5887,7 +5920,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -5898,7 +5931,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -5909,7 +5942,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -5920,7 +5953,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -6019,7 +6052,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -6030,7 +6063,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -6041,7 +6074,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -6052,7 +6085,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -6063,7 +6096,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -6074,7 +6107,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>174</v>
       </c>
@@ -6085,7 +6118,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -6096,7 +6129,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -6107,7 +6140,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -6118,7 +6151,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>178</v>
       </c>
@@ -6129,7 +6162,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -6140,7 +6173,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>180</v>
       </c>
@@ -6151,7 +6184,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -6162,7 +6195,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>182</v>
       </c>
@@ -6173,7 +6206,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -6184,7 +6217,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>184</v>
       </c>
@@ -6283,7 +6316,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -6294,7 +6327,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>194</v>
       </c>
@@ -6305,7 +6338,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -6316,7 +6349,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -6327,7 +6360,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -6338,7 +6371,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>198</v>
       </c>
@@ -6349,7 +6382,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -6360,7 +6393,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>200</v>
       </c>
@@ -6547,7 +6580,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -6558,7 +6591,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>218</v>
       </c>
@@ -6569,7 +6602,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -6580,7 +6613,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>220</v>
       </c>
@@ -6591,7 +6624,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -6602,7 +6635,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>222</v>
       </c>
@@ -6613,7 +6646,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -6624,7 +6657,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -6723,7 +6756,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -6734,7 +6767,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>234</v>
       </c>
@@ -6745,7 +6778,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -6756,7 +6789,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>236</v>
       </c>
@@ -6767,7 +6800,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -6778,7 +6811,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>238</v>
       </c>
@@ -6789,7 +6822,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -6800,7 +6833,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>240</v>
       </c>
@@ -6811,7 +6844,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -6822,7 +6855,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>242</v>
       </c>
@@ -6833,7 +6866,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -6844,7 +6877,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>244</v>
       </c>
@@ -6855,7 +6888,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -6866,7 +6899,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>246</v>
       </c>
@@ -6877,7 +6910,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -6888,7 +6921,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>248</v>
       </c>
@@ -7163,7 +7196,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>273</v>
       </c>
@@ -7174,7 +7207,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>274</v>
       </c>
@@ -7185,7 +7218,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>275</v>
       </c>
@@ -7196,7 +7229,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>276</v>
       </c>
@@ -7207,7 +7240,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>277</v>
       </c>
@@ -7218,7 +7251,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>278</v>
       </c>
@@ -7229,7 +7262,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>279</v>
       </c>
@@ -7240,7 +7273,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A281" s="2">
         <v>280</v>
       </c>
@@ -7251,7 +7284,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="2">
         <v>281</v>
       </c>
@@ -7691,7 +7724,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>321</v>
       </c>
@@ -7702,7 +7735,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>322</v>
       </c>
@@ -7713,7 +7746,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>323</v>
       </c>
@@ -7724,7 +7757,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>324</v>
       </c>
@@ -7735,7 +7768,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>325</v>
       </c>
@@ -7746,7 +7779,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>326</v>
       </c>
@@ -7757,7 +7790,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>327</v>
       </c>
@@ -7768,7 +7801,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>328</v>
       </c>
@@ -7856,7 +7889,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>336</v>
       </c>
@@ -8164,7 +8197,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A365" s="2">
         <v>364</v>
       </c>
@@ -8175,7 +8208,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
         <v>365</v>
       </c>
@@ -8186,7 +8219,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
         <v>366</v>
       </c>
@@ -8197,7 +8230,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
         <v>367</v>
       </c>
@@ -8208,7 +8241,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
         <v>368</v>
       </c>
@@ -8219,7 +8252,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
         <v>369</v>
       </c>
@@ -8230,7 +8263,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
         <v>370</v>
       </c>
@@ -8241,7 +8274,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A372" s="2">
         <v>371</v>
       </c>
@@ -8252,7 +8285,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A373" s="2">
         <v>372</v>
       </c>
@@ -8263,7 +8296,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A374" s="2">
         <v>373</v>
       </c>
@@ -8274,7 +8307,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A375" s="2">
         <v>374</v>
       </c>
@@ -8285,7 +8318,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A376" s="2">
         <v>375</v>
       </c>
@@ -8296,7 +8329,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
         <v>376</v>
       </c>
@@ -8307,7 +8340,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
         <v>377</v>
       </c>
@@ -8318,7 +8351,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A379" s="2">
         <v>378</v>
       </c>
@@ -8329,7 +8362,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A380" s="2">
         <v>379</v>
       </c>
@@ -8340,7 +8373,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A381" s="2">
         <v>380</v>
       </c>
@@ -8351,7 +8384,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="382" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A382" s="2">
         <v>381</v>
       </c>
@@ -8362,7 +8395,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A383" s="2">
         <v>382</v>
       </c>
@@ -8373,7 +8406,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A384" s="2">
         <v>383</v>
       </c>
@@ -8384,7 +8417,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A385" s="2">
         <v>384</v>
       </c>
@@ -8472,7 +8505,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A393" s="2">
         <v>399</v>
       </c>
@@ -8483,7 +8516,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A394" s="2">
         <v>400</v>
       </c>
@@ -8494,7 +8527,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
         <v>401</v>
       </c>
@@ -8505,7 +8538,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A396" s="2">
         <v>402</v>
       </c>
@@ -8516,7 +8549,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A397" s="2">
         <v>403</v>
       </c>
@@ -8527,7 +8560,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A398" s="2">
         <v>404</v>
       </c>
@@ -8538,7 +8571,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A399" s="2">
         <v>405</v>
       </c>
@@ -8780,7 +8813,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="421" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" s="2">
         <v>427</v>
       </c>
@@ -9319,7 +9352,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="470" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A470" s="2">
         <v>476</v>
       </c>
@@ -9330,7 +9363,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="471" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A471" s="2">
         <v>477</v>
       </c>
@@ -9341,7 +9374,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="472" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A472" s="2">
         <v>478</v>
       </c>
@@ -9352,7 +9385,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A473" s="2">
         <v>479</v>
       </c>
@@ -9363,7 +9396,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="474" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A474" s="2">
         <v>480</v>
       </c>
@@ -9374,7 +9407,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="475" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A475" s="2">
         <v>481</v>
       </c>
@@ -9385,7 +9418,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="476" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A476" s="2">
         <v>482</v>
       </c>
@@ -9396,7 +9429,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="477" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A477" s="2">
         <v>483</v>
       </c>
@@ -9550,7 +9583,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="491" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A491" s="2">
         <v>497</v>
       </c>
@@ -9627,7 +9660,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="498" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A498" s="2">
         <v>504</v>
       </c>
@@ -9638,7 +9671,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="499" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A499" s="2">
         <v>505</v>
       </c>
@@ -9649,7 +9682,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="500" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A500" s="2">
         <v>506</v>
       </c>
@@ -9660,7 +9693,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="501" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A501" s="2">
         <v>507</v>
       </c>
@@ -9671,7 +9704,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="502" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A502" s="2">
         <v>508</v>
       </c>
@@ -9682,7 +9715,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="503" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A503" s="2">
         <v>509</v>
       </c>
@@ -10012,7 +10045,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="533" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533" s="2">
         <v>539</v>
       </c>
@@ -10243,7 +10276,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="554" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" s="2">
         <v>560</v>
       </c>
@@ -10254,7 +10287,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="555" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" s="2">
         <v>561</v>
       </c>
@@ -10551,7 +10584,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="582" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582" s="2">
         <v>588</v>
       </c>
@@ -10562,7 +10595,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="583" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" s="2">
         <v>589</v>
       </c>
@@ -11629,7 +11662,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="680" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A680" s="2">
         <v>686</v>
       </c>
@@ -11706,7 +11739,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="687" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A687" s="2">
         <v>693</v>
       </c>
@@ -12014,7 +12047,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="715" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A715" s="2">
         <v>763</v>
       </c>
@@ -12025,7 +12058,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="716" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A716" s="2">
         <v>764</v>
       </c>
@@ -12036,7 +12069,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="717" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A717" s="2">
         <v>765</v>
       </c>
@@ -12047,7 +12080,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="718" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A718" s="2">
         <v>766</v>
       </c>
@@ -12058,7 +12091,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="719" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A719" s="2">
         <v>767</v>
       </c>
@@ -12069,7 +12102,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="720" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A720" s="2">
         <v>768</v>
       </c>
@@ -12080,7 +12113,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="721" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A721" s="2">
         <v>769</v>
       </c>
@@ -12168,7 +12201,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="729" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A729" s="2">
         <v>777</v>
       </c>
@@ -12179,7 +12212,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="730" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A730" s="2">
         <v>778</v>
       </c>
@@ -12190,7 +12223,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="731" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A731" s="2">
         <v>779</v>
       </c>
@@ -12201,7 +12234,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="732" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A732" s="2">
         <v>780</v>
       </c>
@@ -12212,7 +12245,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="733" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A733" s="2">
         <v>781</v>
       </c>
@@ -12223,7 +12256,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="734" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A734" s="2">
         <v>782</v>
       </c>
@@ -12234,7 +12267,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="735" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A735" s="2">
         <v>783</v>
       </c>
@@ -12322,7 +12355,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="743" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A743" s="2">
         <v>791</v>
       </c>
@@ -12333,7 +12366,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="744" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A744" s="2">
         <v>792</v>
       </c>
@@ -12344,7 +12377,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="745" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A745" s="2">
         <v>793</v>
       </c>
@@ -12355,7 +12388,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="746" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A746" s="2">
         <v>794</v>
       </c>
@@ -12366,7 +12399,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="747" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A747" s="2">
         <v>795</v>
       </c>
@@ -12377,7 +12410,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="748" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A748" s="2">
         <v>796</v>
       </c>
@@ -12388,7 +12421,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="749" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A749" s="2">
         <v>797</v>
       </c>
@@ -12399,7 +12432,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="750" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A750" s="2">
         <v>798</v>
       </c>
@@ -12410,7 +12443,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="751" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A751" s="2">
         <v>799</v>
       </c>
@@ -12421,7 +12454,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="752" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A752" s="2">
         <v>800</v>
       </c>
@@ -12432,7 +12465,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="753" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A753" s="2">
         <v>801</v>
       </c>
@@ -12443,7 +12476,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="754" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A754" s="2">
         <v>802</v>
       </c>
@@ -12454,7 +12487,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="755" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A755" s="2">
         <v>803</v>
       </c>
@@ -12465,7 +12498,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="756" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A756" s="2">
         <v>804</v>
       </c>
@@ -12630,7 +12663,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="771" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A771" s="2">
         <v>819</v>
       </c>
@@ -12641,7 +12674,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="772" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A772" s="2">
         <v>820</v>
       </c>
@@ -12652,7 +12685,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="773" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A773" s="2">
         <v>821</v>
       </c>
@@ -12663,7 +12696,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="774" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A774" s="2">
         <v>822</v>
       </c>
@@ -12674,7 +12707,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="775" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A775" s="2">
         <v>823</v>
       </c>
@@ -12685,7 +12718,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="776" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A776" s="2">
         <v>824</v>
       </c>
@@ -12696,7 +12729,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="777" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A777" s="2">
         <v>825</v>
       </c>
@@ -12784,7 +12817,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="785" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A785" s="2">
         <v>833</v>
       </c>
@@ -13015,7 +13048,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="806" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A806" s="2">
         <v>854</v>
       </c>
@@ -13246,7 +13279,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="827" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A827" s="2">
         <v>875</v>
       </c>
@@ -13257,7 +13290,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="828" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A828" s="2">
         <v>876</v>
       </c>
@@ -13268,7 +13301,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="829" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A829" s="2">
         <v>877</v>
       </c>
@@ -13279,7 +13312,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="830" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A830" s="2">
         <v>878</v>
       </c>
@@ -13290,7 +13323,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="831" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A831" s="2">
         <v>879</v>
       </c>
@@ -13301,7 +13334,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="832" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A832" s="2">
         <v>880</v>
       </c>
@@ -13312,7 +13345,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="833" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A833" s="2">
         <v>881</v>
       </c>
@@ -13323,7 +13356,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="834" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A834" s="2">
         <v>882</v>
       </c>
@@ -13334,7 +13367,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="835" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A835" s="2">
         <v>883</v>
       </c>
@@ -13345,7 +13378,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="836" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A836" s="2">
         <v>884</v>
       </c>
@@ -13356,7 +13389,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="837" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A837" s="2">
         <v>885</v>
       </c>
@@ -13367,7 +13400,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="838" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A838" s="2">
         <v>886</v>
       </c>
@@ -13378,7 +13411,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="839" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A839" s="2">
         <v>887</v>
       </c>
@@ -13389,7 +13422,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="840" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A840" s="2">
         <v>888</v>
       </c>
@@ -13862,7 +13895,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="883" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A883" s="2">
         <v>931</v>
       </c>
@@ -13939,7 +13972,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="890" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A890" s="2">
         <v>938</v>
       </c>
@@ -14093,7 +14126,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="904" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A904" s="2">
         <v>952</v>
       </c>
@@ -14247,7 +14280,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="918" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A918" s="2">
         <v>966</v>
       </c>
@@ -14324,7 +14357,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="925" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A925" s="2">
         <v>973</v>
       </c>
@@ -14555,7 +14588,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="946" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="946" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A946" s="2">
         <v>994</v>
       </c>
@@ -14566,7 +14599,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="947" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="947" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A947" s="2">
         <v>995</v>
       </c>
@@ -14588,7 +14621,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="949" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="949" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A949" s="2">
         <v>997</v>
       </c>
@@ -14599,7 +14632,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="950" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A950" s="2">
         <v>998</v>
       </c>
@@ -14621,7 +14654,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="952" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A952" s="2">
         <v>1000</v>
       </c>
@@ -15148,7 +15181,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="996" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="996" spans="1:3" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A996">
         <f t="shared" si="0"/>
         <v>1044</v>
@@ -15231,6 +15264,61 @@
         <v>1183</v>
       </c>
     </row>
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1003">
+        <v>1051</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C1003" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1004">
+        <v>1052</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C1004" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1005">
+        <v>1053</v>
+      </c>
+      <c r="B1005" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C1005" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1006">
+        <v>1054</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C1006" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1007">
+        <v>1055</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>1192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
